--- a/CBT_2025_4회/산업안전기사_2025_4회_문항등록.xlsx
+++ b/CBT_2025_4회/산업안전기사_2025_4회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="AG4" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Phase 0 은 무의식·실신 상태&lt;/strong&gt;다. 주의작용이 전혀 없고 신뢰성은 0 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;의식수준의 다섯 단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;의식상태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;주의작용&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;신뢰성&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Phase 0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;무의식 · 실신&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;없음(zero)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Phase Ⅰ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;의식이 흐릿함&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;활발하지 않음&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.9 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Phase Ⅱ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이완 상태&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;수동적&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.99 ~ 0.99999&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Phase Ⅲ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상쾌한 상태&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;적극적&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.99999 이상&lt;/u&gt; — 가장 높다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Phase Ⅳ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;과긴장 · 흥분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;한 점에 집중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.9 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;Phase 0은 무의식·실신 상태&lt;/strong&gt;다. 주의작용이 전혀 없고 신뢰성은 0이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;의식수준의 다섯 단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;의식상태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;주의작용&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;신뢰성&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Phase 0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;무의식 · 실신&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;없음(zero)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Phase Ⅰ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;의식이 흐릿함&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;활발하지 않음&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.9 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Phase Ⅱ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이완 상태&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;수동적&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.99 ~ 0.99999&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Phase Ⅲ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상쾌한 상태&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;적극적&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.99999 이상&lt;/u&gt; — 가장 높다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Phase Ⅳ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;과긴장 · 흥분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;한 점에 집중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.9 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH4" s="32" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="AI4" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;의식수준(Phase)의 단계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;Phase Ⅲ 가 가장 신뢰성이 높다&lt;/strong&gt;. 그 아래(Ⅰ·Ⅱ)도, 그 위(Ⅳ)도 떨어진다. &lt;strong&gt;긴장이 지나쳐도 오히려 나빠진다&lt;/strong&gt;는 것이 핵심이며, 동기부여의 「뒤집힌 U 자」와 같은 결이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;Phase 0 은 무의식&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;의식수준(Phase)의 단계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;Phase Ⅲ 가 가장 신뢰성이 높다&lt;/strong&gt;. 그 아래(Ⅰ·Ⅱ)도, 그 위(Ⅳ)도 떨어진다. &lt;strong&gt;긴장이 지나쳐도 오히려 나빠진다&lt;/strong&gt;는 것이 핵심이며, 동기부여의 「뒤집힌 U 자」와 같은 결이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;Phase 0은 무의식&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AI7" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;브레인스토밍의 4원칙&lt;/strong&gt;&lt;br&gt;네 보기가 &lt;strong&gt;4원칙 하나씩에 정확히 대응&lt;/strong&gt; 한다. 세 개는 원칙을 뒤집어 놓았고 하나만 그대로다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비판금지 · 자유분방 · 대량발언 · 수정발언&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;브레인스토밍의 4원칙&lt;/strong&gt;&lt;br&gt;네 보기가 &lt;strong&gt;4원칙 하나씩에 정확히 대응&lt;/strong&gt;한다. 세 개는 원칙을 뒤집어 놓았고 하나만 그대로다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비판금지 · 자유분방 · 대량발언 · 수정발언&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AI9" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;블레이크(Blake)와 머튼(Mouton)의 관리 그리드&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;앞이 생산, 뒤가 인간&lt;/strong&gt;이다. 이 순서만 잡으면 다섯 유형이 모두 풀린다. &lt;strong&gt;9.9형(팀형)이 가장 바람직&lt;/strong&gt; 하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;앞은 과업, 뒤는 사람&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;블레이크(Blake)와 머튼(Mouton)의 관리 그리드&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;앞이 생산, 뒤가 인간&lt;/strong&gt;이다. 이 순서만 잡으면 다섯 유형이 모두 풀린다. &lt;strong&gt;9.9형(팀형)이 가장 바람직&lt;/strong&gt;하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;앞은 과업, 뒤는 사람&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="AG14" s="32" t="inlineStr">
         <is>
-          <t>법정 교육은 &lt;strong&gt;최소 기준&lt;/strong&gt; 일 뿐이다. &lt;strong&gt;그 사업장에 필요한 교육을 더 해야&lt;/strong&gt; 한다.</t>
+          <t>법정 교육은 &lt;strong&gt;최소 기준&lt;/strong&gt;일 뿐이다. &lt;strong&gt;그 사업장에 필요한 교육을 더 해야&lt;/strong&gt; 한다.</t>
         </is>
       </c>
       <c r="AH14" s="32" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AG18" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;설치가 끝난 날부터 3년 이내&lt;/strong&gt;에 최초 안전검사를 하고, 그 뒤로는 &lt;strong&gt;2년마다&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전검사의 주기&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최초 검사&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;그 뒤&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;크레인 · 리프트 · 곤돌라&lt;/u&gt;&lt;/td&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설치 끝난 날부터 3년 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2년마다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;건설현장은 6개월마다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이동식 크레인 · 이삿짐운반용 리프트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;신규등록 뒤 3년 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2년마다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;프레스 · 전단기 · 압력용기 · 원심기 · 롤러기 등&lt;/u&gt;&lt;/td&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설치 끝난 날부터 3년 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2년마다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공정안전보고서 확인 결과가 우수하면 4년마다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;설치가 끝난 날부터 3년 이내&lt;/strong&gt;에 최초 안전검사를 하고, 그 뒤로는 &lt;strong&gt;2년마다&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전검사의 주기&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최초 검사&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;그 뒤&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;크레인 · 리프트 · 곤돌라&lt;/u&gt;&lt;/td&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설치 끝난 날부터 3년 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2년마다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;건설현장은 6개월마다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이동식 크레인 · 이삿짐운반용 리프트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;신규등록 뒤 3년 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2년마다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;프레스 · 전단기 · 압력용기 · 원심기 · 롤러기 등&lt;/u&gt;&lt;/td&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설치 끝난 날부터 3년 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2년마다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;공정안전보고서 확인 결과가 우수하면 4년마다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH18" s="32" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="AI20" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;버드(Bird)의 신연쇄성 이론&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;하인리히는 「불안전한 행동과 상태(제3요인)」를 없애라&lt;/strong&gt; 했고, &lt;strong&gt;버드는 「관리의 부족(제1단계)」을 없애라&lt;/strong&gt; 했다. &lt;strong&gt;뿌리를 어디로 보느냐&lt;/strong&gt;가 두 이론의 차이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;버드는 관리의 부족부터&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;버드(Bird)의 신연쇄성 이론&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;하인리히는 「불안전한 행동과 상태(제3요인)」를 없애라&lt;/strong&gt;했고, &lt;strong&gt;버드는 「관리의 부족(제1단계)」을 없애라&lt;/strong&gt;했다. &lt;strong&gt;뿌리를 어디로 보느냐&lt;/strong&gt;가 두 이론의 차이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;버드는 관리의 부족부터&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AG21" s="32" t="inlineStr">
         <is>
-          <t>연근로시간은 $1 {,} 000 \times 2 {,} 400 = 2 {,} 400 {,} 000$ 시간이다. $\text{도수율} = \dfrac{\text{재해건수}}{\text{연근로시간}} \times 10^{6}$ 이므로 $\text{재해건수} = 10 \times 2 {,} 400 {,} 000 / 10^{6} = 24$ 건이다.&lt;img src="safe_A_2025_04_019_exp1.png"&gt;&lt;em&gt;도수율과 강도율 — 곱하는 수가 다르다&lt;/em&gt;</t>
+          <t>연근로시간은 $1 {,} 000 \times 2 {,} 400 = 2 {,} 400 {,} 000$ 시간이다. $\text{도수율} = \dfrac{\text{재해건수}}{\text{연근로시간}} \times 10^{6}$이므로 $\text{재해건수} = 10 \times 2 {,} 400 {,} 000 / 10^{6} = 24$ 건이다.&lt;img src="safe_A_2025_04_019_exp1.png"&gt;&lt;em&gt;도수율과 강도율 — 곱하는 수가 다르다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH21" s="32" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AG23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;조합 AND 게이트&lt;/strong&gt;다. &lt;strong&gt;n 개 가운데 정해진 k 개가 일어나면&lt;/strong&gt; 출력이 난다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 의 수정게이트&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;게이트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조합 AND&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;n 개 가운데 k 개가 일어나면 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;「어느 것이든 2개」&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;우선적 AND&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정해진 순서대로&lt;/u&gt; 일어나야 출력&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;배타적 OR&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 둘 이상 겹치면 출력이 없다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;「동시 발생이 없음」&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;억제 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조건이 만족될 때만&lt;/u&gt; 출력&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;육각형&lt;/u&gt; 안에 조건&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험지속 기호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 일정 시간 이어져야&lt;/u&gt; 출력&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;조합 AND 게이트&lt;/strong&gt;다. &lt;strong&gt;n 개 가운데 정해진 k 개가 일어나면&lt;/strong&gt; 출력이 난다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA의 수정게이트&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;게이트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조합 AND&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;n 개 가운데 k 개가 일어나면 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;「어느 것이든 2개」&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;우선적 AND&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정해진 순서대로&lt;/u&gt; 일어나야 출력&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;배타적 OR&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 둘 이상 겹치면 출력이 없다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;「동시 발생이 없음」&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;억제 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조건이 만족될 때만&lt;/u&gt; 출력&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;육각형&lt;/u&gt; 안에 조건&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험지속 기호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 일정 시간 이어져야&lt;/u&gt; 출력&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH23" s="32" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="AG24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;시간에 따른 원인 분석&lt;/strong&gt;은 FTA 의 기대효과가 아니다. FTA 는 &lt;strong&gt;특정 시점의 논리 구조&lt;/strong&gt;를 보는 것이지 시간의 흐름을 따라가지 않는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 의 기대효과&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기대효과&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사고원인 규명의 간편화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;논리기호로 한눈에&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사고원인 분석의 일반화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;같은 틀로 여러 사고를&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사고원인 분석의 정량화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;확률 계산이 된다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;노력과 시간의 절감&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시스템의 결함 진단&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전점검 체크리스트 작성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;시간에 따른 원인 분석&lt;/strong&gt;은 FTA의 기대효과가 아니다. FTA는 &lt;strong&gt;특정 시점의 논리 구조&lt;/strong&gt;를 보는 것이지 시간의 흐름을 따라가지 않는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA의 기대효과&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기대효과&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사고원인 규명의 간편화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;논리기호로 한눈에&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사고원인 분석의 일반화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;같은 틀로 여러 사고를&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사고원인 분석의 정량화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;확률 계산이 된다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;노력과 시간의 절감&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시스템의 결함 진단&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전점검 체크리스트 작성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH24" s="32" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AI24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 기대효과&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;시간의 흐름을 따라가는 것은 ETA(사건수 분석)&lt;/strong&gt;다. 초기 사건에서 시작해 &lt;strong&gt;성공과 실패로 갈라지며 시간 순으로&lt;/strong&gt; 전개한다. FTA 와 결이 다르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;시간 흐름은 ETA 쪽&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 기대효과&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;시간의 흐름을 따라가는 것은 ETA(사건수 분석)&lt;/strong&gt;다. 초기 사건에서 시작해 &lt;strong&gt;성공과 실패로 갈라지며 시간 순으로&lt;/strong&gt; 전개한다. FTA와 결이 다르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;시간 흐름은 ETA 쪽&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4656,12 +4656,12 @@
       </c>
       <c r="AG28" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;A 는 근원섬유(근절), B 는 액틴, C 는 마이오신&lt;/strong&gt;이다. &lt;strong&gt;가는 액틴이 굵은 마이오신 사이로 미끄러져 들어가&lt;/strong&gt; 근육이 줄어든다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;근육의 구조와 수축&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;근막&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;근육 전체를 싸는 막&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;수축단위가 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;근섬유&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;근육을 이루는 세포 하나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;근원섬유(근절)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수축의 기본 단위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;A&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;액틴&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가는 필라멘트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;B&lt;/u&gt; — 미끄러져 들어간다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;마이오신&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;굵은 필라멘트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C&lt;/u&gt; — 그 사이로&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;A는 근원섬유(근절), B는 액틴, C는 마이오신&lt;/strong&gt;이다. &lt;strong&gt;가는 액틴이 굵은 마이오신 사이로 미끄러져 들어가&lt;/strong&gt; 근육이 줄어든다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;근육의 구조와 수축&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;근막&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;근육 전체를 싸는 막&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;수축단위가 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;근섬유&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;근육을 이루는 세포 하나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;근원섬유(근절)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수축의 기본 단위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;A&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;액틴&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가는 필라멘트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;B&lt;/u&gt; — 미끄러져 들어간다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;마이오신&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;굵은 필라멘트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C&lt;/u&gt; — 그 사이로&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH28" s="32" t="inlineStr">
         <is>
-          <t>① A 는 근막이 아니라 근원섬유다.&lt;br&gt;② B 와 C 가 서로 바뀌었다.&lt;br&gt;③ B 와 C 가 필라멘트 이름이 아니다.</t>
+          <t>① A는 근막이 아니라 근원섬유다.&lt;br&gt;② B와 C가 서로 바뀌었다.&lt;br&gt;③ B와 C가 필라멘트 이름이 아니다.</t>
         </is>
       </c>
       <c r="AI28" s="32" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="AG30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;「예비조처상태」&lt;/strong&gt;라는 범주는 없다. 네 범주는 &lt;strong&gt;파국적 · 위기적(중대) · 한계적 · 무시가능&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;PHA 의 위험 4범주&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;범주&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파국적(catastrophic)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사망 또는 시스템 완전 손실&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 심각&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위기적·중대(critical)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중대한 상해나 시스템 중대 손상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;즉시 조치 필요&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한계적(marginal)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;경미한 상해, 제어 가능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무시가능(negligible)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상해나 손상이 거의 없다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;「예비조처상태」&lt;/strong&gt;라는 범주는 없다. 네 범주는 &lt;strong&gt;파국적 · 위기적(중대) · 한계적 · 무시가능&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;PHA의 위험 4범주&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;범주&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;파국적(catastrophic)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사망 또는 시스템 완전 손실&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 심각&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위기적·중대(critical)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중대한 상해나 시스템 중대 손상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;즉시 조치 필요&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한계적(marginal)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;경미한 상해, 제어 가능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무시가능(negligible)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상해나 손상이 거의 없다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH30" s="32" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AI30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;예비위험분석(PHA)의 위험 범주&lt;/strong&gt;&lt;br&gt;PHA 는 &lt;strong&gt;시스템 수명주기의 맨 처음(구상단계)&lt;/strong&gt;에 하는 &lt;strong&gt;정성적&lt;/strong&gt; 분석이다. 그래서 이름에 &lt;strong&gt;「예비(preliminary)」&lt;/strong&gt;가 붙었다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;파국 · 위기 · 한계 · 무시가능&lt;/u&gt; 넷.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;예비위험분석(PHA)의 위험 범주&lt;/strong&gt;&lt;br&gt;PHA는 &lt;strong&gt;시스템 수명주기의 맨 처음(구상단계)&lt;/strong&gt;에 하는 &lt;strong&gt;정성적&lt;/strong&gt; 분석이다. 그래서 이름에 &lt;strong&gt;「예비(preliminary)」&lt;/strong&gt;가 붙었다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;파국 · 위기 · 한계 · 무시가능&lt;/u&gt; 넷.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="AH31" s="32" t="inlineStr">
         <is>
-          <t>① HCR 은 인간 인지 신뢰도 평가 방법이다.&lt;br&gt;② THERP 는 인간 과오율 예측기법이다.&lt;br&gt;③ SLIM 은 성공가능성 지수법이다.</t>
+          <t>① HCR은 인간 인지 신뢰도 평가 방법이다.&lt;br&gt;② THERP는 인간 과오율 예측기법이다.&lt;br&gt;③ SLIM은 성공가능성 지수법이다.</t>
         </is>
       </c>
       <c r="AI31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;인간 신뢰도의 평가 방법&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FMEA·FMECA·FTA 는 물적 요소&lt;/strong&gt;를 다루고, &lt;strong&gt;THERP·HCR·SLIM 은 인적 요소&lt;/strong&gt;를 다룬다. &lt;strong&gt;「사람인가 물건인가」&lt;/strong&gt;로 가른다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FMECA 만 설비 쪽&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;인간 신뢰도의 평가 방법&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FMEA·FMECA·FTA는 물적 요소&lt;/strong&gt;를 다루고, &lt;strong&gt;THERP·HCR·SLIM은 인적 요소&lt;/strong&gt;를 다룬다. &lt;strong&gt;「사람인가 물건인가」&lt;/strong&gt;로 가른다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FMECA 만 설비 쪽&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="AG34" s="32" t="inlineStr">
         <is>
-          <t>산소 1 [L] 는 약 5 [kcal] 이므로 작업 에너지는 $1.3 \times 5 = 6.5$ [kcal/min] 이다. $R = \dfrac{T ( E - S )}{E - 1.5}$ 에 $T = 480$, $S = 5$, $E = 6.5$ 을 넣으면 $R = \dfrac{480 \times ( 6.5 - 5 )}{6.5 - 1.5} = \dfrac{720}{5} = 144$ 분이다.</t>
+          <t>산소 1 [L]는 약 5 [kcal]이므로 작업 에너지는 $1.3 \times 5 = 6.5$ [kcal/min]이다. $R = \dfrac{T ( E - S )}{E - 1.5}$에 $T = 480$, $S = 5$, $E = 6.5$을 넣으면 $R = \dfrac{480 \times ( 6.5 - 5 )}{6.5 - 1.5} = \dfrac{720}{5} = 144$ 분이다.</t>
         </is>
       </c>
       <c r="AH34" s="32" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="AI34" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Murrell 의 휴식시간 산정식&lt;/strong&gt;&lt;br&gt;$R = \dfrac{T ( E - S )}{E - 1.5}$ 다. &lt;strong&gt;T 는 총 작업시간(분), E 는 작업의 에너지소비량, S 는 표준 에너지소비량(남성 5 [kcal/min]), 1.5 는 휴식 중 에너지소비량&lt;/strong&gt;이다. &lt;strong&gt;산소 1 [L] = 5 [kcal]&lt;/strong&gt;이라는 환산이 앞에 온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;산소 1 [L] 는 5 [kcal]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;Murrell의 휴식시간 산정식&lt;/strong&gt;&lt;br&gt;$R = \dfrac{T ( E - S )}{E - 1.5}$다. &lt;strong&gt;T는 총 작업시간(분), E는 작업의 에너지소비량, S는 표준 에너지소비량(남성 5 [kcal/min]), 1.5는 휴식 중 에너지소비량&lt;/strong&gt;이다. &lt;strong&gt;산소 1 [L] = 5 [kcal]&lt;/strong&gt;이라는 환산이 앞에 온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;산소 1 [L]는 5 [kcal]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="AI35" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;인체계측 자료의 응용원칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;5 와 95 라는 숫자가 세 원칙 모두에 쓰인다&lt;/strong&gt; — 조절식은 그 사이를, 최대치 설계는 95 를, 최소치 설계는 5 를 쓴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;5 ~ 95 백분위수&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;인체계측 자료의 응용원칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;5와 95라는 숫자가 세 원칙 모두에 쓰인다&lt;/strong&gt; — 조절식은 그 사이를, 최대치 설계는 95를, 최소치 설계는 5를 쓴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;5 ~ 95 백분위수&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AH36" s="32" t="inlineStr">
         <is>
-          <t>① B(천장)가 가장 높아야 하므로 두 번째에 올 수 없다.&lt;br&gt;② B 와 D 의 순서가 어긋난다.&lt;br&gt;④ C 와 D 의 순서가 어긋난다.</t>
+          <t>① B(천장)가 가장 높아야 하므로 두 번째에 올 수 없다.&lt;br&gt;② B와 D의 순서가 어긋난다.&lt;br&gt;④ C와 D의 순서가 어긋난다.</t>
         </is>
       </c>
       <c r="AI36" s="32" t="inlineStr">
@@ -5821,17 +5821,17 @@
       </c>
       <c r="AG37" s="32" t="inlineStr">
         <is>
-          <t>$\text{소요조명} = \dfrac{\text{휘도}}{\text{반사율}} \times 100 = \dfrac{90}{60} \times 100 = 150$ [fc] 다.</t>
+          <t>$\text{소요조명} = \dfrac{\text{휘도}}{\text{반사율}} \times 100 = \dfrac{90}{60} \times 100 = 150$ [fc]다.</t>
         </is>
       </c>
       <c r="AH37" s="32" t="inlineStr">
         <is>
-          <t>① 75 [fc] 는 계산과 맞지 않는다.&lt;br&gt;③ 200 [fc] 도 맞지 않는다.&lt;br&gt;④ 300 [fc] 도 맞지 않는다.</t>
+          <t>① 75 [fc]는 계산과 맞지 않는다.&lt;br&gt;③ 200 [fc] 도 맞지 않는다.&lt;br&gt;④ 300 [fc] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI37" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;반사율과 소요조명&lt;/strong&gt;&lt;br&gt;$\text{반사율} [ \% ] = \dfrac{\text{휘도}}{\text{조도}} \times 100$ 을 조도에 대해 푼 식이다. &lt;strong&gt;반사율이 낮은 대상일수록 더 밝게 비춰야&lt;/strong&gt; 같은 휘도를 얻는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;휘도 ÷ 반사율 × 100&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;반사율과 소요조명&lt;/strong&gt;&lt;br&gt;$\text{반사율} [ \% ] = \dfrac{\text{휘도}}{\text{조도}} \times 100$을 조도에 대해 푼 식이다. &lt;strong&gt;반사율이 낮은 대상일수록 더 밝게 비춰야&lt;/strong&gt; 같은 휘도를 얻는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;휘도 ÷ 반사율 × 100&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5935,13 +5935,13 @@
       <c r="AA38" s="32" t="inlineStr"/>
       <c r="AB38" s="32" t="inlineStr">
         <is>
-          <t>귀는 중음역에 민감하므로 500 ~ 3000Hz 의 진동수를 사용한다.</t>
+          <t>귀는 중음역에 민감하므로 500 ~ 3000Hz의 진동수를 사용한다.</t>
         </is>
       </c>
       <c r="AC38" s="32" t="inlineStr"/>
       <c r="AD38" s="32" t="inlineStr">
         <is>
-          <t>300 m 이상의 장거리용으로는 1000Hz 를 초과하는 진동수를 사용한다.</t>
+          <t>300 m 이상의 장거리용으로는 1000Hz를 초과하는 진동수를 사용한다.</t>
         </is>
       </c>
       <c r="AE38" s="32" t="inlineStr"/>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AH38" s="32" t="inlineStr">
         <is>
-          <t>① 주의 환기를 위해 변조된 신호를 쓰는 것은 맞다.&lt;br&gt;② 배경소음과 다른 진동수를 쓰는 것도 맞다.&lt;br&gt;③ 500 ~ 3,000 [Hz] 를 쓰는 것도 맞다.</t>
+          <t>① 주의 환기를 위해 변조된 신호를 쓰는 것은 맞다.&lt;br&gt;② 배경소음과 다른 진동수를 쓰는 것도 맞다.&lt;br&gt;③ 500 ~ 3,000 [Hz]를 쓰는 것도 맞다.</t>
         </is>
       </c>
       <c r="AI38" s="32" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="AG39" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;동목형&lt;/strong&gt;은 &lt;strong&gt;눈금이 움직이고 바늘이 고정&lt;/strong&gt; 되어 있어, &lt;strong&gt;창(窓)만큼만 보이면 되므로 면적을 줄일 수 있다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정량적 표시장치의 종류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇이 움직이나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;특징&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;동침형(moving pointer)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바늘이 움직이고 눈금이 고정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;변화의 방향과 속도를 알기 쉽다&lt;/u&gt; — 가장 널리 쓰인다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;동목형(moving scale)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;눈금이 움직이고 바늘이 고정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;면적을 줄일 수 있다&lt;/u&gt; · 변화를 알기 어렵다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계수형(digital)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;숫자로 표시&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정확한 값을 읽기에 가장 좋다&lt;/u&gt; · 변화 추세는 못 본다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;동목형&lt;/strong&gt;은 &lt;strong&gt;눈금이 움직이고 바늘이 고정&lt;/strong&gt;되어 있어, &lt;strong&gt;창(窓)만큼만 보이면 되므로 면적을 줄일 수 있다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정량적 표시장치의 종류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇이 움직이나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;특징&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;동침형(moving pointer)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바늘이 움직이고 눈금이 고정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;변화의 방향과 속도를 알기 쉽다&lt;/u&gt; — 가장 널리 쓰인다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;동목형(moving scale)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;눈금이 움직이고 바늘이 고정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;면적을 줄일 수 있다&lt;/u&gt; · 변화를 알기 어렵다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계수형(digital)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;숫자로 표시&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정확한 값을 읽기에 가장 좋다&lt;/u&gt; · 변화 추세는 못 본다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH39" s="32" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="AG40" s="32" t="inlineStr">
         <is>
-          <t>FTA 는 &lt;strong&gt;정성적 분석과 정량적 분석이 모두&lt;/strong&gt; 가능하다. 오히려 &lt;strong&gt;정량화가 되는 것이 FTA 의 강점&lt;/strong&gt;이다.</t>
+          <t>FTA는 &lt;strong&gt;정성적 분석과 정량적 분석이 모두&lt;/strong&gt; 가능하다. 오히려 &lt;strong&gt;정량화가 되는 것이 FTA의 강점&lt;/strong&gt;이다.</t>
         </is>
       </c>
       <c r="AH40" s="32" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="AI40" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 특징&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FTA 는 정량 가능, FMEA 는 정성적&lt;/strong&gt;이다. 「정성적만 가능하다」는 FMEA 의 특징을 FTA 에 갖다 붙인 것이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FTA 는 정량도 된다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 특징&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FTA는 정량 가능, FMEA는 정성적&lt;/strong&gt;이다. 「정성적만 가능하다」는 FMEA의 특징을 FTA에 갖다 붙인 것이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FTA는 정량도 된다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
       <c r="AC41" s="32" t="inlineStr"/>
       <c r="AD41" s="32" t="inlineStr">
         <is>
-          <t>20000 Hz 이상에서 노출 제한은 110 dB 이다.</t>
+          <t>20000 Hz 이상에서 노출 제한은 110 dB이다.</t>
         </is>
       </c>
       <c r="AE41" s="32" t="inlineStr"/>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="AG41" s="32" t="inlineStr">
         <is>
-          <t>초음파 소음은 &lt;strong&gt;3 [dB] 이 아니라 하루 노출한도가 따로&lt;/strong&gt; 정해진다. 우리 기준에서 &lt;strong&gt;5 [dB] 오를 때마다 허용시간이 절반&lt;/strong&gt;이 되는 것은 &lt;strong&gt;가청 소음&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;소음의 허용기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가청 소음(강렬한 소음작업)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;90 [dB] 8시간&lt;/u&gt; — &lt;u&gt;5 [dB] 오르면 절반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;95 → 4시간, 100 → 2시간&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;충격소음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;120 [dB] 초과 1만회 · 130 초과 1천회 · 140 초과 100회&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;초음파 소음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20,000 [Hz] 이상에서 110 [dB] 노출 제한&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가청영역 위&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>초음파 소음은 &lt;strong&gt;3 [dB]이 아니라 하루 노출한도가 따로&lt;/strong&gt; 정해진다. 우리 기준에서 &lt;strong&gt;5 [dB] 오를 때마다 허용시간이 절반&lt;/strong&gt;이 되는 것은 &lt;strong&gt;가청 소음&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;소음의 허용기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가청 소음(강렬한 소음작업)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;90 [dB] 8시간&lt;/u&gt; — &lt;u&gt;5 [dB] 오르면 절반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;95 → 4시간, 100 → 2시간&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;충격소음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;120 [dB] 초과 1만회 · 130 초과 1천회 · 140 초과 100회&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;초음파 소음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20,000 [Hz] 이상에서 110 [dB] 노출 제한&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가청영역 위&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH41" s="32" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="AI41" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;초음파 소음&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;5 [dB] 마다 절반&lt;/strong&gt;이라는 규칙은 &lt;strong&gt;가청 소음&lt;/strong&gt;의 것이다. 보기는 이 숫자만 3 으로 바꿔 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;5 [dB] 마다 절반&lt;/u&gt; — 3 이 아니다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;초음파 소음&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;5 [dB] 마다 절반&lt;/strong&gt;이라는 규칙은 &lt;strong&gt;가청 소음&lt;/strong&gt;의 것이다. 보기는 이 숫자만 3으로 바꿔 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;5 [dB] 마다 절반&lt;/u&gt; — 3이 아니다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="AG48" s="32" t="inlineStr">
         <is>
-          <t>화기를 사용하는 설비로부터 &lt;strong&gt;3 [m] 를 초과하는 장소&lt;/strong&gt;에 설치해야 한다. 1 [m] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;아세틸렌 발생기실의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;건물의 최상층&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;위로 새게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;화기를 사용하는 설비로부터&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3 [m] 를 초과하는 장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m] 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;옥외 설치 시 개구부 ↔ 다른 건축물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.5 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;벽 ↔ 발생기실&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.5 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;불연성 재료 · 철근 콘크리트 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;게이지 압력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;127 [kPa] 초과 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>화기를 사용하는 설비로부터 &lt;strong&gt;3 [m]를 초과하는 장소&lt;/strong&gt;에 설치해야 한다. 1 [m]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;아세틸렌 발생기실의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;건물의 최상층&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;위로 새게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;화기를 사용하는 설비로부터&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3 [m]를 초과하는 장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m]가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;옥외 설치 시 개구부 ↔ 다른 건축물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.5 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;벽 ↔ 발생기실&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.5 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;불연성 재료 · 철근 콘크리트 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;게이지 압력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;127 [kPa] 초과 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH48" s="32" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AI49" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;포터블 벨트 컨베이어의 안전&lt;/strong&gt;&lt;br&gt;바퀴 달린 장비를 옮길 때의 대원칙은 &lt;strong&gt;무게중심을 낮춘 뒤 움직인다&lt;/strong&gt;는 것이다. 지게차가 &lt;strong&gt;포크를 내리고 주행&lt;/strong&gt; 하는 것, 불도저가 &lt;strong&gt;삽날을 내려놓는&lt;/strong&gt; 것과 같은 이치다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;내린 뒤에 옮긴다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;포터블 벨트 컨베이어의 안전&lt;/strong&gt;&lt;br&gt;바퀴 달린 장비를 옮길 때의 대원칙은 &lt;strong&gt;무게중심을 낮춘 뒤 움직인다&lt;/strong&gt;는 것이다. 지게차가 &lt;strong&gt;포크를 내리고 주행&lt;/strong&gt;하는 것, 불도저가 &lt;strong&gt;삽날을 내려놓는&lt;/strong&gt; 것과 같은 이치다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;내린 뒤에 옮긴다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="AI52" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;셰이퍼(형삭기)의 방호장치&lt;/strong&gt;&lt;br&gt;셰이퍼는 &lt;strong&gt;램이 앞뒤로 왕복&lt;/strong&gt; 하며 깎는 기계라 &lt;strong&gt;협착점&lt;/strong&gt;이 생긴다. 그래서 방호장치가 모두 &lt;strong&gt;램에 다가가지 못하게 막는&lt;/strong&gt; 쪽이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;급속귀환장치는 능률용&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;셰이퍼(형삭기)의 방호장치&lt;/strong&gt;&lt;br&gt;셰이퍼는 &lt;strong&gt;램이 앞뒤로 왕복&lt;/strong&gt;하며 깎는 기계라 &lt;strong&gt;협착점&lt;/strong&gt;이 생긴다. 그래서 방호장치가 모두 &lt;strong&gt;램에 다가가지 못하게 막는&lt;/strong&gt; 쪽이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;급속귀환장치는 능률용&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="AG59" s="32" t="inlineStr">
         <is>
-          <t>하역작업 시 좌우 안정도는 &lt;strong&gt;6 [%] 이내&lt;/strong&gt;다. 10 [%] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차의 안정도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안정도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 — 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5톤 이상은 3.5 [%]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 — 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [%] 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 — 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;18 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 — 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;(15 + 1.1V) [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;V 는 [km/h]&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2025_04_057_exp1.png"&gt;&lt;em&gt;지게차 안정도 — 하역은 작고 주행은 크다&lt;/em&gt;</t>
+          <t>하역작업 시 좌우 안정도는 &lt;strong&gt;6 [%] 이내&lt;/strong&gt;다. 10 [%]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차의 안정도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안정도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 — 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5톤 이상은 3.5 [%]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 — 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [%]가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 — 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;18 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 — 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;(15 + 1.1V) [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;V는 [km/h]&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2025_04_057_exp1.png"&gt;&lt;em&gt;지게차 안정도 — 하역은 작고 주행은 크다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH59" s="32" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="U63" s="32" t="inlineStr">
         <is>
-          <t>인체저항을 500Ω이라 한다면, 심실세동을 일으키는 위험한계 에너지는 약 몇 J 인가? (단, 심실세동전류값 I = 165/√T mA 의 Dalziel의 식을 이용하며, 통전시간은 1초로 한다.)</t>
+          <t>인체저항을 500Ω이라 한다면, 심실세동을 일으키는 위험한계 에너지는 약 몇 J 인가? (단, 심실세동전류값 I = 165/√T mA의 Dalziel의 식을 이용하며, 통전시간은 1초로 한다.)</t>
         </is>
       </c>
       <c r="V63" s="32" t="inlineStr"/>
@@ -9175,17 +9175,17 @@
       </c>
       <c r="AG63" s="32" t="inlineStr">
         <is>
-          <t>$W = I^{2} R T = ( 165 \times 10^{-3} )^{2} \times 500 \times 1 = 0.027225 \times 500 \fallingdotseq 13.6$ [J] 이다.</t>
+          <t>$W = I^{2} R T = ( 165 \times 10^{-3} )^{2} \times 500 \times 1 = 0.027225 \times 500 \fallingdotseq 13.6$ [J]이다.</t>
         </is>
       </c>
       <c r="AH63" s="32" t="inlineStr">
         <is>
-          <t>① 11.5 [J] 는 계산과 맞지 않는다.&lt;br&gt;③ 15.3 [J] 도 맞지 않는다.&lt;br&gt;④ 16.2 [J] 도 맞지 않는다.</t>
+          <t>① 11.5 [J]는 계산과 맞지 않는다.&lt;br&gt;③ 15.3 [J] 도 맞지 않는다.&lt;br&gt;④ 16.2 [J] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI63" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;심실세동 한계에너지&lt;/strong&gt;&lt;br&gt;$I = 165 / \sqrt{T}$ 를 넣으면 $T$&lt;strong&gt; 가 약분되어 사라진다&lt;/strong&gt;. 그래서 &lt;strong&gt;통전시간과 무관하게 저항 500 [Ω] 에서는 언제나 약 13.6 [J]&lt;/strong&gt;이 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;500 [Ω] 이면 13.6 [J]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;심실세동 한계에너지&lt;/strong&gt;&lt;br&gt;$I = 165 / \sqrt{T}$를 넣으면 $T$&lt;strong&gt;가 약분되어 사라진다&lt;/strong&gt;. 그래서 &lt;strong&gt;통전시간과 무관하게 저항 500 [Ω] 에서는 언제나 약 13.6 [J]&lt;/strong&gt;이 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;500 [Ω] 이면 13.6 [J]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="AG64" s="32" t="inlineStr">
         <is>
-          <t>물에 젖으면 &lt;strong&gt;약 1/25 로&lt;/strong&gt; 떨어진다. 1/12 는 &lt;strong&gt;땀에 젖었을 때&lt;/strong&gt;의 값이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인체저항이 떨어지는 정도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;저항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;건조한 피부&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 2,500 [Ω]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;내부 저항은 약 500 [Ω]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;땀에 젖은 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1/12&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;약 200 [Ω]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물에 젖은 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1/25&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1/12 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;땀에 젖고 물에도 젖은 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1/25 보다 더&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>물에 젖으면 &lt;strong&gt;약 1/25로&lt;/strong&gt; 떨어진다. 1/12는 &lt;strong&gt;땀에 젖었을 때&lt;/strong&gt;의 값이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인체저항이 떨어지는 정도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;저항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;건조한 피부&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 2,500 [Ω]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;내부 저항은 약 500 [Ω]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;땀에 젖은 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1/12&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;약 200 [Ω]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물에 젖은 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1/25&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1/12가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;땀에 젖고 물에도 젖은 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1/25보다 더&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH64" s="32" t="inlineStr">
@@ -9433,12 +9433,12 @@
       </c>
       <c r="AG65" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;15 [mA], 0.03초 이내&lt;/strong&gt;다. 물기가 있으면 &lt;strong&gt;인체 저항이 1/25 로 떨어져&lt;/strong&gt; 기준을 절반으로 낮춘다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누전차단기의 정격감도전류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;설치 장소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;정격감도전류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;동작시간&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일반 장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [mA] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.03초 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물기 있는 장소&lt;/u&gt; (욕실·화장실 등)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;15 [mA] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.03초 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;15 [mA], 0.03초 이내&lt;/strong&gt;다. 물기가 있으면 &lt;strong&gt;인체 저항이 1/25로 떨어져&lt;/strong&gt; 기준을 절반으로 낮춘다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누전차단기의 정격감도전류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;설치 장소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;정격감도전류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;동작시간&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일반 장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [mA] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.03초 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물기 있는 장소&lt;/u&gt; (욕실·화장실 등)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;15 [mA] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.03초 이내&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH65" s="32" t="inlineStr">
         <is>
-          <t>① 30 [mA] 는 일반 장소의 기준이며 0.01초라는 시간도 없다.&lt;br&gt;② 30 [mA] 는 물기 있는 장소의 기준이 아니다.&lt;br&gt;③ 동작시간은 0.01초가 아니라 0.03초다.</t>
+          <t>① 30 [mA]는 일반 장소의 기준이며 0.01초라는 시간도 없다.&lt;br&gt;② 30 [mA]는 물기 있는 장소의 기준이 아니다.&lt;br&gt;③ 동작시간은 0.01초가 아니라 0.03초다.</t>
         </is>
       </c>
       <c r="AI65" s="32" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="AI66" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;전격 위험도의 결정 인자&lt;/strong&gt;&lt;br&gt;전압은 &lt;strong&gt;인체저항과 함께 전류를 만드는 재료&lt;/strong&gt; 일 뿐이다. 같은 전압이라도 &lt;strong&gt;젖어 있으면 전류가 25배&lt;/strong&gt;로 커진다. 결국 &lt;strong&gt;몸에 실제로 흐른 전류&lt;/strong&gt;가 위험을 정한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전압이 아니라 전류 · 시간 · 경로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;전격 위험도의 결정 인자&lt;/strong&gt;&lt;br&gt;전압은 &lt;strong&gt;인체저항과 함께 전류를 만드는 재료&lt;/strong&gt;일 뿐이다. 같은 전압이라도 &lt;strong&gt;젖어 있으면 전류가 25배&lt;/strong&gt;로 커진다. 결국 &lt;strong&gt;몸에 실제로 흐른 전류&lt;/strong&gt;가 위험을 정한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전압이 아니라 전류 · 시간 · 경로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="U70" s="32" t="inlineStr">
         <is>
-          <t>인체의 전기저항 R을 1000Ω 이라고 할 때 위험 한계 에너지의 최저는 약 몇 J 인가? (단, 통전 시간은 1초이고, 심실세동전류 I = 165/√T mA 이다.)</t>
+          <t>인체의 전기저항 R을 1000Ω 이라고 할 때 위험 한계 에너지의 최저는 약 몇 J 인가? (단, 통전 시간은 1초이고, 심실세동전류 I = 165/√T mA이다.)</t>
         </is>
       </c>
       <c r="V70" s="32" t="inlineStr"/>
@@ -10078,17 +10078,17 @@
       </c>
       <c r="AG70" s="32" t="inlineStr">
         <is>
-          <t>$W = I^{2} R T = ( 165 \times 10^{-3} )^{2} \times 1 {,} 000 \times 1 = 0.027225 \times 1 {,} 000 \fallingdotseq 27.2$ [J] 이다.</t>
+          <t>$W = I^{2} R T = ( 165 \times 10^{-3} )^{2} \times 1 {,} 000 \times 1 = 0.027225 \times 1 {,} 000 \fallingdotseq 27.2$ [J]이다.</t>
         </is>
       </c>
       <c r="AH70" s="32" t="inlineStr">
         <is>
-          <t>① 17.23 [J] 는 계산과 맞지 않는다.&lt;br&gt;③ 37.23 [J] 도 맞지 않는다.&lt;br&gt;④ 47.23 [J] 도 맞지 않는다.</t>
+          <t>① 17.23 [J]는 계산과 맞지 않는다.&lt;br&gt;③ 37.23 [J] 도 맞지 않는다.&lt;br&gt;④ 47.23 [J] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI70" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;심실세동 한계에너지&lt;/strong&gt;&lt;br&gt;61번과 짝이다. &lt;strong&gt;저항이 두 배(500 → 1,000)면 에너지도 두 배(13.6 → 27.2)&lt;/strong&gt;다. $W = I^{2} R T$ 에서 &lt;strong&gt;에너지가 저항에 비례&lt;/strong&gt; 하기 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1,000 [Ω] 이면 27.2 [J]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;심실세동 한계에너지&lt;/strong&gt;&lt;br&gt;61번과 짝이다. &lt;strong&gt;저항이 두 배(500 → 1,000)면 에너지도 두 배(13.6 → 27.2)&lt;/strong&gt;다. $W = I^{2} R T$에서 &lt;strong&gt;에너지가 저항에 비례&lt;/strong&gt;하기 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1,000 [Ω] 이면 27.2 [J]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="AG71" s="32" t="inlineStr">
         <is>
-          <t>안전증 방폭구조의 기호는 &lt;strong&gt;e&lt;/strong&gt;다. &lt;strong&gt;s 는 특수방폭구조&lt;/strong&gt;의 기호다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방폭구조와 기호&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구조&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;영문&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원리&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;d&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;flameproof&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안에서 터져도 밖으로 안 샌다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;압력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;p&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;pressurized&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;깨끗한 공기를 밀어 넣는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;유입&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;o&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;oil-immersed&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;기름 속에 담근다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전증&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;e&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;increased safety&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;s 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;본질안전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ia · ib&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;intrinsic safety&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;에너지를 낮춘다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;몰드&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;m&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;moulded&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;수지로 굳힌다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;충전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;q&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;powder filled&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;모래로 채운다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비점화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;n&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;non-sparking&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2종 장소용&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;특수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;s&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;special&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>안전증 방폭구조의 기호는 &lt;strong&gt;e&lt;/strong&gt;다. &lt;strong&gt;s는 특수방폭구조&lt;/strong&gt;의 기호다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방폭구조와 기호&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구조&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;영문&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원리&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;d&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;flameproof&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안에서 터져도 밖으로 안 샌다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;압력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;p&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;pressurized&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;깨끗한 공기를 밀어 넣는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;유입&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;o&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;oil-immersed&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;기름 속에 담근다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전증&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;e&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;increased safety&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;s가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;본질안전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ia · ib&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;intrinsic safety&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;에너지를 낮춘다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;몰드&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;m&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;moulded&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;수지로 굳힌다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;충전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;q&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;powder filled&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;모래로 채운다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비점화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;n&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;non-sparking&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2종 장소용&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;특수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;s&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;special&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH71" s="32" t="inlineStr">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="AI71" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방폭구조의 기호&lt;/strong&gt;&lt;br&gt;영문 첫 글자로 새긴다 — &lt;strong&gt;d(flameproof) · p(pressurized) · o(oil) · e(increased safety) · m(moulded) · q(quartz/powder) · n(non-sparking) · s(special)&lt;/strong&gt;. &lt;strong&gt;e 와 s 를 바꿔 놓는&lt;/strong&gt; 것이 단골 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;안전증은 e, 특수는 s&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방폭구조의 기호&lt;/strong&gt;&lt;br&gt;영문 첫 글자로 새긴다 — &lt;strong&gt;d(flameproof) · p(pressurized) · o(oil) · e(increased safety) · m(moulded) · q(quartz/powder) · n(non-sparking) · s(special)&lt;/strong&gt;. &lt;strong&gt;e와 s를 바꿔 놓는&lt;/strong&gt; 것이 단골 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;안전증은 e, 특수는 s&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="AG72" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;자기융착성 테이프&lt;/strong&gt;다. 감아 두면 &lt;strong&gt;스스로 녹아 붙어 틈 없이 밀봉&lt;/strong&gt; 되므로 분진이 들어가지 못한다.</t>
+          <t>&lt;strong&gt;자기융착성 테이프&lt;/strong&gt;다. 감아 두면 &lt;strong&gt;스스로 녹아 붙어 틈 없이 밀봉&lt;/strong&gt;되므로 분진이 들어가지 못한다.</t>
         </is>
       </c>
       <c r="AH72" s="32" t="inlineStr">
@@ -10470,7 +10470,7 @@
       </c>
       <c r="AH73" s="32" t="inlineStr">
         <is>
-          <t>① T5 는 온도등급을 나타낸다.&lt;br&gt;③ p 는 방폭구조를 나타낸다.&lt;br&gt;④ ⅡA 는 폭발등급(기기그룹)을 나타낸다.</t>
+          <t>① T5는 온도등급을 나타낸다.&lt;br&gt;③ p는 방폭구조를 나타낸다.&lt;br&gt;④ ⅡA는 폭발등급(기기그룹)을 나타낸다.</t>
         </is>
       </c>
       <c r="AI73" s="32" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="AH74" s="32" t="inlineStr">
         <is>
-          <t>① 30 [cm] 로는 사람이 설 수 없다.&lt;br&gt;② 50 [cm] 도 기준에 못 미친다.&lt;br&gt;④ 100 [cm] 는 기준보다 넓다.</t>
+          <t>① 30 [cm] 로는 사람이 설 수 없다.&lt;br&gt;② 50 [cm] 도 기준에 못 미친다.&lt;br&gt;④ 100 [cm]는 기준보다 넓다.</t>
         </is>
       </c>
       <c r="AI74" s="32" t="inlineStr">
@@ -10981,17 +10981,17 @@
       </c>
       <c r="AG77" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;1.0 [MΩ] 이상&lt;/strong&gt;이다. 380 [V] 는 &lt;strong&gt;FELV 또는 500 [V] 이하&lt;/strong&gt; 구간에 든다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;저압전로의 절연저항 (KEC 132)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;전로의 사용전압&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;DC 시험전압&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;절연저항&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;SELV 및 PELV&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;250 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.5 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FELV, 500 [V] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;500 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.0 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;500 [V] 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.0 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;1.0 [MΩ] 이상&lt;/strong&gt;이다. 380 [V]는 &lt;strong&gt;FELV 또는 500 [V] 이하&lt;/strong&gt; 구간에 든다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;저압전로의 절연저항 (KEC 132)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;전로의 사용전압&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;DC 시험전압&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;절연저항&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;SELV 및 PELV&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;250 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.5 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FELV, 500 [V] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;500 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.0 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;500 [V] 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.0 [MΩ] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH77" s="32" t="inlineStr">
         <is>
-          <t>① 0.2 [MΩ] 은 옛 기준(대지전압 300 [V] 이하)의 값이다.&lt;br&gt;② 0.3 [MΩ] 은 어느 기준에도 없다.&lt;br&gt;③ 0.5 [MΩ] 은 SELV·PELV 의 값이다.</t>
+          <t>① 0.2 [MΩ]은 옛 기준(대지전압 300 [V] 이하)의 값이다.&lt;br&gt;② 0.3 [MΩ]은 어느 기준에도 없다.&lt;br&gt;③ 0.5 [MΩ]은 SELV·PELV의 값이다.</t>
         </is>
       </c>
       <c r="AI77" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;한국전기설비규정(KEC) 132 — 전로의 절연저항&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;0.5 · 1.0 · 1.0&lt;/strong&gt; 세 값뿐이다. &lt;strong&gt;500 [V] 를 넘어도 절연저항은 1.0 [MΩ] 그대로&lt;/strong&gt;이고 &lt;strong&gt;시험전압만 1,000 [V] 로 올라간다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0.5 · 1.0 · 1.0&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 옛 기준(전기설비기술기준)은 &lt;u&gt;대지전압 150 [V] 이하 0.1 [MΩ] · 300 [V] 이하 0.2 [MΩ] · 400 [V] 미만 0.3 [MΩ] · 400 [V] 이상 0.4 [MΩ]&lt;/u&gt; 이었으나, &lt;u&gt;2021. 1. 1. KEC 시행&lt;/u&gt;으로 위 표처럼 바뀌었다. 옛 숫자를 외우고 있으면 틀린다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;한국전기설비규정(KEC) 132 — 전로의 절연저항&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;0.5 · 1.0 · 1.0&lt;/strong&gt; 세 값뿐이다. &lt;strong&gt;500 [V]를 넘어도 절연저항은 1.0 [MΩ] 그대로&lt;/strong&gt;이고 &lt;strong&gt;시험전압만 1,000 [V]로 올라간다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0.5 · 1.0 · 1.0&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 옛 기준(전기설비기술기준)은 &lt;u&gt;대지전압 150 [V] 이하 0.1 [MΩ] · 300 [V] 이하 0.2 [MΩ] · 400 [V] 미만 0.3 [MΩ] · 400 [V] 이상 0.4 [MΩ]&lt;/u&gt; 이었으나, &lt;u&gt;2021. 1. 1. KEC 시행&lt;/u&gt;으로 위 표처럼 바뀌었다. 옛 숫자를 외우고 있으면 틀린다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11110,17 +11110,17 @@
       </c>
       <c r="AG78" s="32" t="inlineStr">
         <is>
-          <t>$\text{여유도} = \dfrac{\text{충격절연강도} - \text{제한전압}}{\text{제한전압}} \times 100 = \dfrac{1 {,} 000 - 800}{800} \times 100 = 25$ [%] 다.</t>
+          <t>$\text{여유도} = \dfrac{\text{충격절연강도} - \text{제한전압}}{\text{제한전압}} \times 100 = \dfrac{1 {,} 000 - 800}{800} \times 100 = 25$ [%]다.</t>
         </is>
       </c>
       <c r="AH78" s="32" t="inlineStr">
         <is>
-          <t>② 33 [%] 는 분모를 잘못 잡았을 때 나온다.&lt;br&gt;③ 47 [%] 는 계산과 맞지 않는다.&lt;br&gt;④ 63 [%] 도 맞지 않는다.</t>
+          <t>② 33 [%]는 분모를 잘못 잡았을 때 나온다.&lt;br&gt;③ 47 [%]는 계산과 맞지 않는다.&lt;br&gt;④ 63 [%] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI78" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;피뢰기의 보호여유도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분모가 제한전압&lt;/strong&gt;이라는 점이 갈림길이다. 충격절연강도로 나누면 20 [%] 가 나와 오답이 된다. 실무에서는 &lt;strong&gt;20 [%] 이상&lt;/strong&gt;을 확보한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;(BIL − 제한전압) ÷ 제한전압&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;피뢰기의 보호여유도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분모가 제한전압&lt;/strong&gt;이라는 점이 갈림길이다. 충격절연강도로 나누면 20 [%]가 나와 오답이 된다. 실무에서는 &lt;strong&gt;20 [%] 이상&lt;/strong&gt;을 확보한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;(BIL − 제한전압) ÷ 제한전압&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="AH79" s="32" t="inlineStr">
         <is>
-          <t>① 다심코드 0.75 [㎟] 이상은 제3종·특별 제3종의 기준이다.&lt;br&gt;② 다심캡타이어 케이블 2.5 [㎟] 라는 기준은 없다.&lt;br&gt;③ 4 [㎟] 이상이라는 기준도 없다.</t>
+          <t>① 다심코드 0.75 [㎟] 이상은 제3종·특별 제3종의 기준이다.&lt;br&gt;② 다심캡타이어 케이블 2.5 [㎟]라는 기준은 없다.&lt;br&gt;③ 4 [㎟] 이상이라는 기준도 없다.</t>
         </is>
       </c>
       <c r="AI79" s="32" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="AG83" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;아세톤&lt;/strong&gt;이다. 아세틸렌은 그대로 압축하면 &lt;strong&gt;분해폭발&lt;/strong&gt; 하므로, 용기에 &lt;strong&gt;다공성 물질(규조토 등)&lt;/strong&gt;을 채우고 &lt;strong&gt;아세톤에 녹여&lt;/strong&gt; 담는다.</t>
+          <t>&lt;strong&gt;아세톤&lt;/strong&gt;이다. 아세틸렌은 그대로 압축하면 &lt;strong&gt;분해폭발&lt;/strong&gt;하므로, 용기에 &lt;strong&gt;다공성 물질(규조토 등)&lt;/strong&gt;을 채우고 &lt;strong&gt;아세톤에 녹여&lt;/strong&gt; 담는다.</t>
         </is>
       </c>
       <c r="AH83" s="32" t="inlineStr">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="AI83" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;아세틸렌의 용해 저장&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;아세톤 1 [L] 에 아세틸렌이 약 25 [L] 녹는다&lt;/strong&gt;(15 [℃], 1기압). 이 때문에 &lt;strong&gt;용기를 눕히면 아세톤이 함께 흘러나와&lt;/strong&gt; 위험해지므로 &lt;strong&gt;반드시 세워서&lt;/strong&gt; 쓴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;아세톤에 녹여 다공질에 담는다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;아세틸렌의 용해 저장&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;아세톤 1 [L]에 아세틸렌이 약 25 [L] 녹는다&lt;/strong&gt;(15 [℃], 1기압). 이 때문에 &lt;strong&gt;용기를 눕히면 아세톤이 함께 흘러나와&lt;/strong&gt; 위험해지므로 &lt;strong&gt;반드시 세워서&lt;/strong&gt; 쓴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;아세톤에 녹여 다공질에 담는다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="AG84" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;이산화질소(NO₂)&lt;/strong&gt;다. $4 \mathrm{HNO}_{3} \rightarrow 4 NO_{2} + 2 H_{2} O + O_{2}$ 로 &lt;strong&gt;적갈색 유독 기체&lt;/strong&gt;가 나온다.</t>
+          <t>&lt;strong&gt;이산화질소(NO₂)&lt;/strong&gt;다. $4 \mathrm{HNO}_{3} \rightarrow 4 NO_{2} + 2 H_{2} O + O_{2}$로 &lt;strong&gt;적갈색 유독 기체&lt;/strong&gt;가 나온다.</t>
         </is>
       </c>
       <c r="AH84" s="32" t="inlineStr">
@@ -12014,12 +12014,12 @@
       </c>
       <c r="AH85" s="32" t="inlineStr">
         <is>
-          <t>① 사이클로헥산은 1.3 ~ 8 [vol%] 로 좁다.&lt;br&gt;③ 수소는 상한이 75 [vol%] 로 산화에틸렌보다 낮다.&lt;br&gt;④ 이황화탄소는 상한이 44 [vol%] 다.</t>
+          <t>① 사이클로헥산은 1.3 ~ 8 [vol%]로 좁다.&lt;br&gt;③ 수소는 상한이 75 [vol%]로 산화에틸렌보다 낮다.&lt;br&gt;④ 이황화탄소는 상한이 44 [vol%]다.</t>
         </is>
       </c>
       <c r="AI85" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;주요 가스의 폭발범위&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;상한이 80 [%] 를 넘는 것은 아세틸렌(81)과 산화에틸렌(80)&lt;/strong&gt; 둘뿐이다. 둘 다 &lt;strong&gt;공기 없이도 스스로 분해하며 터지는&lt;/strong&gt; 분해폭발성 물질이라는 공통점이 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;산화에틸렌 3 ~ 80&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;주요 가스의 폭발범위&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;상한이 80 [%]를 넘는 것은 아세틸렌(81)과 산화에틸렌(80)&lt;/strong&gt; 둘뿐이다. 둘 다 &lt;strong&gt;공기 없이도 스스로 분해하며 터지는&lt;/strong&gt; 분해폭발성 물질이라는 공통점이 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;산화에틸렌 3 ~ 80&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12148,7 +12148,7 @@
       </c>
       <c r="AI86" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;자연발화의 조건과 방지법&lt;/strong&gt;&lt;br&gt;자연발화는 &lt;strong&gt;발열 &amp;gt; 방열&lt;/strong&gt; 일 때 일어난다. 발열의 종류로는 &lt;strong&gt;산화열(건성유·석탄) · 분해열(질화면) · 미생물열(퇴비) · 흡착열(활성탄) · 중합열(단량체)&lt;/strong&gt;이 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;습도는 낮게&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;자연발화의 조건과 방지법&lt;/strong&gt;&lt;br&gt;자연발화는 &lt;strong&gt;발열 &amp;gt; 방열&lt;/strong&gt;일 때 일어난다. 발열의 종류로는 &lt;strong&gt;산화열(건성유·석탄) · 분해열(질화면) · 미생물열(퇴비) · 흡착열(활성탄) · 중합열(단량체)&lt;/strong&gt;이 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;습도는 낮게&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12401,12 +12401,12 @@
       </c>
       <c r="AH88" s="32" t="inlineStr">
         <is>
-          <t>① 벤젠은 −11 [℃] 다.&lt;br&gt;② 메탄올은 11 [℃] 다.&lt;br&gt;④ 경유는 50 ~ 70 [℃] 다.</t>
+          <t>① 벤젠은 −11 [℃]다.&lt;br&gt;② 메탄올은 11 [℃]다.&lt;br&gt;④ 경유는 50 ~ 70 [℃]다.</t>
         </is>
       </c>
       <c r="AI88" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;인화점의 크기 비교&lt;/strong&gt;&lt;br&gt;이황화탄소는 &lt;strong&gt;인화점 −30 [℃] 에 최소발화에너지 0.009 [mJ]&lt;/strong&gt;로 둘 다 가장 위험한 축이다. 그래서 &lt;strong&gt;물속에 저장하고 유속을 1 [m/s] 이하&lt;/strong&gt;로 제한한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;이황화탄소 −30 [℃]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;인화점의 크기 비교&lt;/strong&gt;&lt;br&gt;이황화탄소는 &lt;strong&gt;인화점 −30 [℃]에 최소발화에너지 0.009 [mJ]&lt;/strong&gt;로 둘 다 가장 위험한 축이다. 그래서 &lt;strong&gt;물속에 저장하고 유속을 1 [m/s] 이하&lt;/strong&gt;로 제한한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;이황화탄소 −30 [℃]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="U89" s="32" t="inlineStr">
         <is>
-          <t>프로판(C3H8) 가스가 공기 중 연소할 때의 화학양론농도는 약 얼마인가? (단, 공기 중의 산소농도는 21vol% 이다.)</t>
+          <t>프로판(C3H8) 가스가 공기 중 연소할 때의 화학양론농도는 약 얼마인가? (단, 공기 중의 산소농도는 21vol%이다.)</t>
         </is>
       </c>
       <c r="V89" s="32" t="inlineStr"/>
@@ -12525,17 +12525,17 @@
       </c>
       <c r="AG89" s="32" t="inlineStr">
         <is>
-          <t>$C_{\mathrm{st}} = \dfrac{100}{1 + 4.773 ( n + \dfrac{m}{4} )}$ 다. 프로판은 $3 + 8 / 4 = 5$ 이므로 $C_{\mathrm{st}} = 100 / ( 1 + 4.773 \times 5 ) = 100 / 24.87 \fallingdotseq 4.02$ [vol%] 다.</t>
+          <t>$C_{\mathrm{st}} = \dfrac{100}{1 + 4.773 ( n + \dfrac{m}{4} )}$다. 프로판은 $3 + 8 / 4 = 5$이므로 $C_{\mathrm{st}} = 100 / ( 1 + 4.773 \times 5 ) = 100 / 24.87 \fallingdotseq 4.02$ [vol%]다.</t>
         </is>
       </c>
       <c r="AH89" s="32" t="inlineStr">
         <is>
-          <t>① 2.5 [vol%] 는 계산과 맞지 않는다.&lt;br&gt;③ 5.6 [vol%] 도 맞지 않는다.&lt;br&gt;④ 9.5 [vol%] 는 프로판의 폭발상한계 값이다.</t>
+          <t>① 2.5 [vol%]는 계산과 맞지 않는다.&lt;br&gt;③ 5.6 [vol%] 도 맞지 않는다.&lt;br&gt;④ 9.5 [vol%]는 프로판의 폭발상한계 값이다.</t>
         </is>
       </c>
       <c r="AI89" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;화학양론조성($C_{\mathrm{st}}$)&lt;/strong&gt;&lt;br&gt;4.773 은 $1 / 0.21$ 에서 나왔다. &lt;strong&gt;메탄은 9.5, 프로판은 4.0&lt;/strong&gt;으로 &lt;strong&gt;탄소가 많을수록 낮아진다&lt;/strong&gt; — 산소가 더 많이 필요하기 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $C_{\mathrm{st}} = 100 \div ( 1 + 4.773 \times ( n + m / 4 ) )$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;화학양론조성($C_{\mathrm{st}}$)&lt;/strong&gt;&lt;br&gt;4.773은 $1 / 0.21$에서 나왔다. &lt;strong&gt;메탄은 9.5, 프로판은 4.0&lt;/strong&gt;으로 &lt;strong&gt;탄소가 많을수록 낮아진다&lt;/strong&gt; — 산소가 더 많이 필요하기 때문이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $C_{\mathrm{st}} = 100 \div ( 1 + 4.773 \times ( n + m / 4 ) )$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="AG91" s="32" t="inlineStr">
         <is>
-          <t>칼륨 화재에 &lt;strong&gt;이산화탄소를 쓰면 안 된다&lt;/strong&gt;. $4 K + 3 CO_{2} \rightarrow 2 K_{2} CO_{3} + C$ 로 &lt;strong&gt;이산화탄소를 분해하며 계속 탄다&lt;/strong&gt;. &lt;strong&gt;건조사나 팽창질석&lt;/strong&gt;으로 덮어야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;금속화재(D급)에 쓸 수 없는 소화약제&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;약제&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;왜 안 되나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소를 내며 폭발&lt;/u&gt; 한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이산화탄소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;금속이 CO₂ 를 분해&lt;/u&gt; 하며 탄다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;할론&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;금속과 반응&lt;/u&gt; 한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;건조사 · 팽창질석 · 금속화재용 분말&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;덮어서 산소를 끊는다&lt;/u&gt; — 이것만 가능&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>칼륨 화재에 &lt;strong&gt;이산화탄소를 쓰면 안 된다&lt;/strong&gt;. $4 K + 3 CO_{2} \rightarrow 2 K_{2} CO_{3} + C$로 &lt;strong&gt;이산화탄소를 분해하며 계속 탄다&lt;/strong&gt;. &lt;strong&gt;건조사나 팽창질석&lt;/strong&gt;으로 덮어야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;금속화재(D급)에 쓸 수 없는 소화약제&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;약제&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;왜 안 되나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수소를 내며 폭발&lt;/u&gt;한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이산화탄소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;금속이 CO₂ 를 분해&lt;/u&gt;하며 탄다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;할론&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;금속과 반응&lt;/u&gt;한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;건조사 · 팽창질석 · 금속화재용 분말&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;덮어서 산소를 끊는다&lt;/u&gt; — 이것만 가능&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH91" s="32" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="AG93" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;질소&lt;/strong&gt;다. 고압에서 &lt;strong&gt;혈액에 녹아 있던 질소가 감압 때 기포가 되어&lt;/strong&gt; 혈관을 막는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;이상기압에 의한 장해&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;감압병(잠함병·잠수병)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;녹아 있던 질소가 기포가 된다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;천천히 감압&lt;/u&gt; 하면 막을 수 있다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;질소마취&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고압의 질소가 마취 작용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;수심 30 [m] 넘으면&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산소중독&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고압의 산소가 독으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고산병&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;저압에서 산소 부족&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;반대 방향&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;질소&lt;/strong&gt;다. 고압에서 &lt;strong&gt;혈액에 녹아 있던 질소가 감압 때 기포가 되어&lt;/strong&gt; 혈관을 막는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;이상기압에 의한 장해&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;감압병(잠함병·잠수병)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;녹아 있던 질소가 기포가 된다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;천천히 감압&lt;/u&gt;하면 막을 수 있다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;질소마취&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고압의 질소가 마취 작용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;수심 30 [m] 넘으면&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산소중독&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고압의 산소가 독으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고산병&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;저압에서 산소 부족&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;반대 방향&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH93" s="32" t="inlineStr">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="AI93" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;감압병(잠함병)&lt;/strong&gt;&lt;br&gt;원리는 &lt;strong&gt;탄산음료의 뚜껑을 여는 것&lt;/strong&gt;과 같다. 압력이 갑자기 낮아지면 녹아 있던 기체가 거품이 된다. 그래서 &lt;strong&gt;천천히 감압&lt;/strong&gt; 하는 것이 유일한 예방책이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;감압병은 질소 기포&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;감압병(잠함병)&lt;/strong&gt;&lt;br&gt;원리는 &lt;strong&gt;탄산음료의 뚜껑을 여는 것&lt;/strong&gt;과 같다. 압력이 갑자기 낮아지면 녹아 있던 기체가 거품이 된다. 그래서 &lt;strong&gt;천천히 감압&lt;/strong&gt;하는 것이 유일한 예방책이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;감압병은 질소 기포&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13136,7 +13136,7 @@
       </c>
       <c r="U94" s="32" t="inlineStr">
         <is>
-          <t>할론 소화약제 중 Halon 2402 의 화학식으로 옳은 것은?</t>
+          <t>할론 소화약제 중 Halon 2402의 화학식으로 옳은 것은?</t>
         </is>
       </c>
       <c r="V94" s="32" t="inlineStr"/>
@@ -13567,7 +13567,7 @@
       </c>
       <c r="AI97" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제283조 — 건조설비의 사용&lt;/strong&gt;&lt;br&gt;건조물이 이탈해 &lt;strong&gt;가열부에 떨어지면 그대로 발화&lt;/strong&gt; 한다. 그래서 「쉽게 이탈되지 않도록」이 조문의 표현이다. &lt;strong&gt;「~되도록」과 「~되지 않도록」&lt;/strong&gt;을 뒤집는 것이 단골 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;이탈되지 않도록&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C283%EC%A1%B0" target="_blank"&gt;제283조(건조설비의 사용)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 건조설비를 사용하여 작업을 하는 경우에 폭발이나 화재를 예방하기 위하여 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 위험물 건조설비를 사용하는 경우에는 미리 내부를 청소하거나 환기할 것&lt;br&gt; 2. 위험물 건조설비를 사용하는 경우에는 건조로 인하여 발생하는 가스ㆍ증기 또는 분진에 의하여 폭발ㆍ화재의 위험이 있는 물질을 안전한 장소로 배출시킬 것&lt;br&gt;▶  3. &lt;strong&gt;위험물 건조설비를 사용하여 가열건조하는 건조물은 쉽게 이탈되지 않도록&lt;/strong&gt; 할 것&lt;br&gt; 4. 고온으로 가열건조한 인화성 액체는 발화의 위험이 없는 온도로 냉각한 후에 격납시킬 것&lt;br&gt; 5. 건조설비(바깥 면이 현저히 고온이 되는 설비만 해당한다)에 가까운 장소에는 인화성 액체를 두지 않도록 할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제283조 — 건조설비의 사용&lt;/strong&gt;&lt;br&gt;건조물이 이탈해 &lt;strong&gt;가열부에 떨어지면 그대로 발화&lt;/strong&gt;한다. 그래서 「쉽게 이탈되지 않도록」이 조문의 표현이다. &lt;strong&gt;「~되도록」과 「~되지 않도록」&lt;/strong&gt;을 뒤집는 것이 단골 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;이탈되지 않도록&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C283%EC%A1%B0" target="_blank"&gt;제283조(건조설비의 사용)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 건조설비를 사용하여 작업을 하는 경우에 폭발이나 화재를 예방하기 위하여 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 위험물 건조설비를 사용하는 경우에는 미리 내부를 청소하거나 환기할 것&lt;br&gt; 2. 위험물 건조설비를 사용하는 경우에는 건조로 인하여 발생하는 가스ㆍ증기 또는 분진에 의하여 폭발ㆍ화재의 위험이 있는 물질을 안전한 장소로 배출시킬 것&lt;br&gt;▶  3. &lt;strong&gt;위험물 건조설비를 사용하여 가열건조하는 건조물은 쉽게 이탈되지 않도록&lt;/strong&gt; 할 것&lt;br&gt; 4. 고온으로 가열건조한 인화성 액체는 발화의 위험이 없는 온도로 냉각한 후에 격납시킬 것&lt;br&gt; 5. 건조설비(바깥 면이 현저히 고온이 되는 설비만 해당한다)에 가까운 장소에는 인화성 액체를 두지 않도록 할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -13929,13 +13929,13 @@
       <c r="AA100" s="32" t="inlineStr"/>
       <c r="AB100" s="32" t="inlineStr">
         <is>
-          <t>비중이 0.79 이므로 물보다 가볍다.</t>
+          <t>비중이 0.79이므로 물보다 가볍다.</t>
         </is>
       </c>
       <c r="AC100" s="32" t="inlineStr"/>
       <c r="AD100" s="32" t="inlineStr">
         <is>
-          <t>인화점이 20°C 이므로 여름철에 더 인화 위험이 높다.</t>
+          <t>인화점이 20°C이므로 여름철에 더 인화 위험이 높다.</t>
         </is>
       </c>
       <c r="AE100" s="32" t="inlineStr"/>
@@ -13944,17 +13944,17 @@
       </c>
       <c r="AG100" s="32" t="inlineStr">
         <is>
-          <t>아세톤의 인화점은 &lt;strong&gt;−18 [℃]&lt;/strong&gt;다. 20 [℃] 가 아니며, &lt;strong&gt;겨울에도 증기가 나와 늘 위험&lt;/strong&gt; 하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;아세톤의 성질&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;값&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인화점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−18 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20 [℃] 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발화점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;465 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭발범위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5 ~ 12.8 [vol%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.79&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물보다 가볍다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;증기비중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;공기보다 무겁다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물 용해도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;잘 녹는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;아세틸렌 용제로도 쓴다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>아세톤의 인화점은 &lt;strong&gt;−18 [℃]&lt;/strong&gt;다. 20 [℃]가 아니며, &lt;strong&gt;겨울에도 증기가 나와 늘 위험&lt;/strong&gt;하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;아세톤의 성질&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;값&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인화점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−18 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20 [℃]가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발화점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;465 [℃]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭발범위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5 ~ 12.8 [vol%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.79&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물보다 가볍다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;증기비중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;공기보다 무겁다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물 용해도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;잘 녹는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;아세틸렌 용제로도 쓴다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH100" s="32" t="inlineStr">
         <is>
-          <t>① 증기가 유독하므로 흡입하지 않도록 주의해야 하는 것은 맞다.&lt;br&gt;② 무색이고 휘발성이 강한 액체인 것도 맞다.&lt;br&gt;③ 비중 0.79 로 물보다 가벼운 것도 맞다.</t>
+          <t>① 증기가 유독하므로 흡입하지 않도록 주의해야 하는 것은 맞다.&lt;br&gt;② 무색이고 휘발성이 강한 액체인 것도 맞다.&lt;br&gt;③ 비중 0.79로 물보다 가벼운 것도 맞다.</t>
         </is>
       </c>
       <c r="AI100" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;아세톤(CH₃COCH₃)의 성질&lt;/strong&gt;&lt;br&gt;아세톤은 &lt;strong&gt;인화점이 영하라 계절을 가리지 않고 위험&lt;/strong&gt; 하다. &lt;strong&gt;물에 잘 녹아&lt;/strong&gt; 아세틸렌 용제로 쓰이고, &lt;strong&gt;증기비중 2.0&lt;/strong&gt;이라 증기가 바닥에 깔린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;아세톤 인화점 −18 [℃]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;아세톤(CH₃COCH₃)의 성질&lt;/strong&gt;&lt;br&gt;아세톤은 &lt;strong&gt;인화점이 영하라 계절을 가리지 않고 위험&lt;/strong&gt;하다. &lt;strong&gt;물에 잘 녹아&lt;/strong&gt; 아세틸렌 용제로 쓰이고, &lt;strong&gt;증기비중 2.0&lt;/strong&gt;이라 증기가 바닥에 깔린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;아세톤 인화점 −18 [℃]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14336,7 +14336,7 @@
       </c>
       <c r="AH103" s="32" t="inlineStr">
         <is>
-          <t>① 띠장 방향은 1.85 [m] 이하, 장선 방향은 1.5 [m] 이하다.&lt;br&gt;② 띠장 간격은 1.8 [m] 가 아니라 2.0 [m] 이하다.&lt;br&gt;④ 21 [m] 가 아니라 31 [m] 되는 지점 아래다.</t>
+          <t>① 띠장 방향은 1.85 [m] 이하, 장선 방향은 1.5 [m] 이하다.&lt;br&gt;② 띠장 간격은 1.8 [m]가 아니라 2.0 [m] 이하다.&lt;br&gt;④ 21 [m]가 아니라 31 [m] 되는 지점 아래다.</t>
         </is>
       </c>
       <c r="AI103" s="32" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="AH104" s="32" t="inlineStr">
         <is>
-          <t>① 80 [kgf] 는 어느 칸에도 없다.&lt;br&gt;② 110 [kgf] 는 5 [cm] 매듭 있는 방망의 신품 값이다.&lt;br&gt;③ 150 [kgf] 는 10 [cm] 매듭 없는 방망의 폐기 값이다.</t>
+          <t>① 80 [kgf]는 어느 칸에도 없다.&lt;br&gt;② 110 [kgf]는 5 [cm] 매듭 있는 방망의 신품 값이다.&lt;br&gt;③ 150 [kgf]는 10 [cm] 매듭 없는 방망의 폐기 값이다.</t>
         </is>
       </c>
       <c r="AI104" s="32" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="AI105" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;추락방호망의 표시&lt;/strong&gt;&lt;br&gt;표시 사항은 모두 &lt;strong&gt;언제 만들었고 얼마나 세며 언제 버려야 하는가&lt;/strong&gt;를 알려 준다. &lt;strong&gt;정기시험은 사용 개시 후 1년 이내, 그 뒤 6개월마다&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;제조자명 · 제조연월 · 재봉 치수 · 그물코 · 신품 강도&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;추락방호망의 표시&lt;/strong&gt;&lt;br&gt;표시 사항은 모두 &lt;strong&gt;언제 만들었고 얼마나 세며 언제 버려야 하는가&lt;/strong&gt;를 알려 준다. &lt;strong&gt;정기시험은 사용 개시 후 1년 이내, 그 뒤 6개월마다&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;제조자명 · 제조연월 · 재봉 치수 · 그물코 · 신품 강도&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14722,17 +14722,17 @@
       </c>
       <c r="AG106" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;A 는 3개, B 는 4개&lt;/strong&gt;다. &lt;strong&gt;3개 이상 이어 쓰지 않고, 이을 때는 볼트 4개 이상&lt;/strong&gt;으로 조인다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;파이프 서포트 동바리의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;까닭&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이어서 쓰는 개수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3개 이상 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이을수록 좌굴에 약하다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이을 때 볼트·전용철물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4개 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이음부가 벌어지지 않게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 3.5 [m] 초과 시&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [m] 이내마다 수평연결재 2방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;중간을 잡아 준다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;A는 3개, B는 4개&lt;/strong&gt;다. &lt;strong&gt;3개 이상 이어 쓰지 않고, 이을 때는 볼트 4개 이상&lt;/strong&gt;으로 조인다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;파이프 서포트 동바리의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;까닭&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이어서 쓰는 개수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3개 이상 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이을수록 좌굴에 약하다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이을 때 볼트·전용철물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4개 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이음부가 벌어지지 않게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 3.5 [m] 초과 시&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [m] 이내마다 수평연결재 2방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;중간을 잡아 준다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH106" s="32" t="inlineStr">
         <is>
-          <t>① A 가 2개면 두 개도 이을 수 없게 되어 지나치게 엄격하다.&lt;br&gt;③ A 와 B 가 서로 바뀌었다.&lt;br&gt;④ A 가 4개면 세 개까지 이을 수 있게 되어 기준과 다르다.</t>
+          <t>① A가 2개면 두 개도 이을 수 없게 되어 지나치게 엄격하다.&lt;br&gt;③ A와 B가 서로 바뀌었다.&lt;br&gt;④ A가 4개면 세 개까지 이을 수 있게 되어 기준과 다르다.</t>
         </is>
       </c>
       <c r="AI106" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제332조 — 거푸집 동바리 조립 시 안전조치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;3 과 4&lt;/strong&gt;를 짝으로 잡는다 — &lt;strong&gt;이어 쓰는 개수는 3(금지), 조이는 볼트는 4(이상)&lt;/strong&gt;. 두 숫자를 바꿔 놓는 것이 단골 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;이음 3개 금지, 볼트 4개 이상&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C332%EC%A1%B0" target="_blank"&gt;제332조(동바리 조립 시의 안전조치)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 동바리를 조립하는 경우에는 하중의 지지상태를 유지할 수 있도록 다음 각 호의 사항을 준수해야 한다.&lt;br&gt; 1. 받침목이나 깔판의 사용, 콘크리트 타설, 말뚝박기 등 동바리의 침하를 방지하기 위한 조치를 할 것&lt;br&gt; 2. 동바리의 상하 고정 및 미끄러짐 방지 조치를 할 것&lt;br&gt; 3. 상부ㆍ하부의 동바리가 동일 수직선상에 위치하도록 하여 깔판ㆍ받침목에 고정시킬 것&lt;br&gt; 4. 개구부 상부에 동바리를 설치하는 경우에는 상부하중을 견딜 수 있는 견고한 받침대를 설치할 것&lt;br&gt; 5. U헤드 등의 단판이 없는 동바리의 상단에 멍에 등을 올릴 경우에는 해당 상단에 U헤드 등의 단판을 설치하고, 멍에 등이 전도되거나 이탈되지 않도록 고정시킬 것&lt;br&gt; 6. 동바리의 이음은 같은 품질의 재료를 사용할 것&lt;br&gt; 7. 강재의 접속부 및 교차부는 볼트ㆍ클램프 등 전용철물을 사용하여 단단히 연결할 것&lt;br&gt; 8. 거푸집의 형상에 따른 부득이한 경우를 제외하고는 깔판이나 받침목은 2단 이상 끼우지 않도록 할 것&lt;br&gt; 9. 깔판이나 받침목을 이어서 사용하는 경우에는 그 깔판ㆍ받침목을 단단히 연결할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제332조 — 거푸집 동바리 조립 시 안전조치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;3과 4&lt;/strong&gt;를 짝으로 잡는다 — &lt;strong&gt;이어 쓰는 개수는 3(금지), 조이는 볼트는 4(이상)&lt;/strong&gt;. 두 숫자를 바꿔 놓는 것이 단골 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;이음 3개 금지, 볼트 4개 이상&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C332%EC%A1%B0" target="_blank"&gt;제332조(동바리 조립 시의 안전조치)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 동바리를 조립하는 경우에는 하중의 지지상태를 유지할 수 있도록 다음 각 호의 사항을 준수해야 한다.&lt;br&gt; 1. 받침목이나 깔판의 사용, 콘크리트 타설, 말뚝박기 등 동바리의 침하를 방지하기 위한 조치를 할 것&lt;br&gt; 2. 동바리의 상하 고정 및 미끄러짐 방지 조치를 할 것&lt;br&gt; 3. 상부ㆍ하부의 동바리가 동일 수직선상에 위치하도록 하여 깔판ㆍ받침목에 고정시킬 것&lt;br&gt; 4. 개구부 상부에 동바리를 설치하는 경우에는 상부하중을 견딜 수 있는 견고한 받침대를 설치할 것&lt;br&gt; 5. U헤드 등의 단판이 없는 동바리의 상단에 멍에 등을 올릴 경우에는 해당 상단에 U헤드 등의 단판을 설치하고, 멍에 등이 전도되거나 이탈되지 않도록 고정시킬 것&lt;br&gt; 6. 동바리의 이음은 같은 품질의 재료를 사용할 것&lt;br&gt; 7. 강재의 접속부 및 교차부는 볼트ㆍ클램프 등 전용철물을 사용하여 단단히 연결할 것&lt;br&gt; 8. 거푸집의 형상에 따른 부득이한 경우를 제외하고는 깔판이나 받침목은 2단 이상 끼우지 않도록 할 것&lt;br&gt; 9. 깔판이나 받침목을 이어서 사용하는 경우에는 그 깔판ㆍ받침목을 단단히 연결할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -15113,12 +15113,12 @@
       </c>
       <c r="AG109" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;A 는 변형, B 는 지반의 침하 유무&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;콘크리트 타설작업 시의 준수사항 (규칙 제334조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;준수사항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업 시작 전 거푸집동바리등의 변형·변위 및 지반의 침하 유무를 점검하고 이상이 있으면 보수할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;A: 변형, B: 지반의 침하 유무&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업 중에는 감시자를 배치하는 등 이상을 발견하면 즉시 작업을 중지하고 근로자를 대피시킬 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;콘크리트 타설작업 시 거푸집 붕괴의 위험이 발생할 우려가 있으면 충분한 보강조치를 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설계도서상의 콘크리트 양생기간을 준수하여 거푸집동바리등을 해체할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;편심이 발생하지 않도록 골고루 분산하여 타설할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;A는 변형, B는 지반의 침하 유무&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;콘크리트 타설작업 시의 준수사항 (규칙 제334조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;준수사항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업 시작 전 거푸집동바리등의 변형·변위 및 지반의 침하 유무를 점검하고 이상이 있으면 보수할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;A: 변형, B: 지반의 침하 유무&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업 중에는 감시자를 배치하는 등 이상을 발견하면 즉시 작업을 중지하고 근로자를 대피시킬 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;콘크리트 타설작업 시 거푸집 붕괴의 위험이 발생할 우려가 있으면 충분한 보강조치를 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설계도서상의 콘크리트 양생기간을 준수하여 거푸집동바리등을 해체할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;편심이 발생하지 않도록 골고루 분산하여 타설할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH109" s="32" t="inlineStr">
         <is>
-          <t>② 「개구부 방호설비」는 이 조문에 나오지 않는다.&lt;br&gt;③ A 는 균열이 아니라 변형이다.&lt;br&gt;④ A 와 B 둘 다 어긋난다.</t>
+          <t>② 「개구부 방호설비」는 이 조문에 나오지 않는다.&lt;br&gt;③ A는 균열이 아니라 변형이다.&lt;br&gt;④ A와 B 둘 다 어긋난다.</t>
         </is>
       </c>
       <c r="AI109" s="32" t="inlineStr">
@@ -15505,7 +15505,7 @@
       </c>
       <c r="AH112" s="32" t="inlineStr">
         <is>
-          <t>① 1 : 1.5 는 옛 보통흙 습지 범위의 값이다.&lt;br&gt;② 1 : 1.1 은 어느 기준에도 없다.&lt;br&gt;④ 1 : 0.5 는 경암의 기준이다.</t>
+          <t>① 1 : 1.5는 옛 보통흙 습지 범위의 값이다.&lt;br&gt;② 1 : 1.1은 어느 기준에도 없다.&lt;br&gt;④ 1 : 0.5는 경암의 기준이다.</t>
         </is>
       </c>
       <c r="AI112" s="32" t="inlineStr">
@@ -15887,7 +15887,7 @@
       </c>
       <c r="AG115" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;추락방지대와 안전블록&lt;/strong&gt;은 &lt;strong&gt;안전그네식에만&lt;/strong&gt; 쓸 수 있다. 떨어질 때 충격이 크므로 &lt;strong&gt;온몸에 힘을 나누는 그네식&lt;/strong&gt; 이라야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전대의 종류와 사용구분&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사용구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;벨트식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1개 걸이용 · U자 걸이용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;허리에만 두른다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전그네식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1개 걸이용 · U자 걸이용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;온몸에 두른다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;추락방지대 · 안전블록&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전그네식에만&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;추락방지대와 안전블록&lt;/strong&gt;은 &lt;strong&gt;안전그네식에만&lt;/strong&gt; 쓸 수 있다. 떨어질 때 충격이 크므로 &lt;strong&gt;온몸에 힘을 나누는 그네식&lt;/strong&gt;이라야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전대의 종류와 사용구분&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사용구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;벨트식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1개 걸이용 · U자 걸이용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;허리에만 두른다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전그네식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1개 걸이용 · U자 걸이용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;온몸에 두른다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;추락방지대 · 안전블록&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전그네식에만&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH115" s="32" t="inlineStr">
@@ -16145,7 +16145,7 @@
       </c>
       <c r="AG117" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;건립작업에 지장이 되는 수목은 제거하거나 이식&lt;/strong&gt; 해야 한다. 「제거해서는 안 된다」는 반대다.</t>
+          <t>&lt;strong&gt;건립작업에 지장이 되는 수목은 제거하거나 이식&lt;/strong&gt;해야 한다. 「제거해서는 안 된다」는 반대다.</t>
         </is>
       </c>
       <c r="AH117" s="32" t="inlineStr">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="AG121" s="32" t="inlineStr">
         <is>
-          <t>대상액은 &lt;strong&gt;재료비 + 직접노무비&lt;/strong&gt;다. 관급자재를 뺀 대상액은 $30 + 35 = 65$ 억원, 관급자재를 넣으면 $85$ 억원이다. &lt;strong&gt;둘 중 작은 값&lt;/strong&gt;을 쓰되, &lt;strong&gt;관급자재를 뺀 금액의 1.2배(78억)&lt;/strong&gt;를 넘지 않도록 한다. 일반건설공사(갑) 50억 이상 요율 1.97 [%] 를 78억에 적용하면 약 &lt;strong&gt;1억 5,366만원&lt;/strong&gt;, 65억에 적용하면 약 &lt;strong&gt;1억 2,805만원&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;관급자재가 있을 때의 계상&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;계산&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;값&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관급자재를 뺀 대상액&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;65억원&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;사급자재비 + 직접노무비&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관급자재를 넣은 대상액&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;85억원&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관급자재를 뺀 금액의 1.2배&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;78억원&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상한&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계상액&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;둘 중 작은 쪽&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;85억 &amp;gt; 78억 이므로 78억 기준&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>대상액은 &lt;strong&gt;재료비 + 직접노무비&lt;/strong&gt;다. 관급자재를 뺀 대상액은 $30 + 35 = 65$ 억원, 관급자재를 넣으면 $85$ 억원이다. &lt;strong&gt;둘 중 작은 값&lt;/strong&gt;을 쓰되, &lt;strong&gt;관급자재를 뺀 금액의 1.2배(78억)&lt;/strong&gt;를 넘지 않도록 한다. 일반건설공사(갑) 50억 이상 요율 1.97 [%]를 78억에 적용하면 약 &lt;strong&gt;1억 5,366만원&lt;/strong&gt;, 65억에 적용하면 약 &lt;strong&gt;1억 2,805만원&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;관급자재가 있을 때의 계상&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;계산&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;값&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관급자재를 뺀 대상액&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;65억원&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;사급자재비 + 직접노무비&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관급자재를 넣은 대상액&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;85억원&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관급자재를 뺀 금액의 1.2배&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;78억원&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상한&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계상액&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;둘 중 작은 쪽&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;85억 &amp;gt; 78억 이므로 78억 기준&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH121" s="32" t="inlineStr">
